--- a/outputs/evaluation/decision/v1/CF_M01/run_3/CF_M01_decision_eval_gt_report.xlsx
+++ b/outputs/evaluation/decision/v1/CF_M01/run_3/CF_M01_decision_eval_gt_report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,49 +471,239 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>CF_M01_AD01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>The goal of this is to improve the security, scalability, and availability of the system.</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>*CF_M01_C07, CF_M01_C04, CF_M01_C02</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>CF_M01_P03</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>42</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Security; Scalability; Availability and reliability</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Service-oriented</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>AD_02</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>En el cas de la plataforma de Waapiti, l’arquitectura física no es correspon exactament a l’arquitectura lògica, ja que tant la capa de negoci com la capa de dades es divideixen en diversos serveis diferents. L’objectiu d’això és millorar la seguretat, l’escalabilitat i la disponibilitat del sistema.</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>0.7478</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>CF_M01_AD02</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Increases system security [...] It is only the Api Gateway that is responsible for authorization and SSL with the client</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>*CF_M01_C07</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>CF_M01_AU10</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>43</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>API Gateway Service</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>AD_03</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Això és degut de què es segueix el patró de disseny de microserveis Api Gateway. Aquest patró de disseny permet que solament un component sigui qui interactuï entre els usuaris i els serveis que proporciona la plataforma.</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>0.733</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
           <t>CF_M01_AD03</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Gives the ability to handle partial system crashes</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>*CF_M01_C08</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>CF_M01_AU10</t>
         </is>
       </c>
-      <c r="E2" t="n">
+      <c r="E4" t="n">
         <v>43</v>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>Resilience</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>API Gateway Service</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>AD_01</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>The physical architecture does not correspond exactly to the logical architecture, as both the business layer and the data layer are divided into several different services. The goal of this is to improve the security, scalability and availability of the system.</t>
-        </is>
-      </c>
-      <c r="J2" t="n">
-        <v>0.6352</v>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>AD_02</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>En el cas de la plataforma de Waapiti, l’arquitectura física no es correspon exactament a l’arquitectura lògica, ja que tant la capa de negoci com la capa de dades es divideixen en diversos serveis diferents. L’objectiu d’això és millorar la seguretat, l’escalabilitat i la disponibilitat del sistema.</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>0.6258</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>CF_M01_AD06</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>In this project, this framework has been used to develop the different services that interact with each other. This framework allows the creation of a secure and complex REST API in an easier way than using NodeJS directly.</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>*CF_M01_C11</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>CF_M01_AU33</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>46</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Maintainability</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>NestJS</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>AD_03</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Això és degut de què es segueix el patró de disseny de microserveis Api Gateway. Aquest patró de disseny permet que solament un component sigui qui interactuï entre els usuaris i els serveis que proporciona la plataforma.</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>0.7117</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>CF_M01_AD07</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>To ensure the fastest possible data transmission, two Amazon services have been used, which allow us to perform a transmission in almost real time.</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>CF_M01_C01</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>CF_M01_AU16</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Speed and latency</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>AWS cloud services set</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>AD_04</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>S’ha decidit la utilització d’AWS i no altres serveis cloud pel seu baix preu i la seva utilització prèvia per part de l’empresa.</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>0.6481</v>
       </c>
     </row>
   </sheetData>
